--- a/excel/UrbanPlanning-Solution.xlsx
+++ b/excel/UrbanPlanning-Solution.xlsx
@@ -5,21 +5,53 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boyko\stats\opt2025\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Boyko Amarov\stats\opt2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75326B3D-A29E-4B6D-9BE7-593086FE0BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5709483-C24B-4C9C-8D11-074EE02FF8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4104" yWindow="3312" windowWidth="17280" windowHeight="9960" xr2:uid="{C6683981-43B6-42B1-A8A0-7AF311EA88D4}"/>
+    <workbookView xWindow="25725" yWindow="0" windowWidth="25980" windowHeight="14400" xr2:uid="{C6683981-43B6-42B1-A8A0-7AF311EA88D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$C$3:$G$3</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">Sheet1!$C$9:$E$9</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">Sheet1!$G$3</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">Sheet1!$I$4:$I$5</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">Sheet1!$I$4:$I$5</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$F$8</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Sheet1!$H$6</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">Sheet1!$C$10:$E$10</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">Sheet1!$G$7</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">Sheet1!$J$4:$J$5</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">Sheet1!$J$4:$J$5</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
@@ -45,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>House types</t>
   </si>
@@ -86,16 +118,13 @@
     <t>Available for demolitions</t>
   </si>
   <si>
-    <t>Total new constructions</t>
-  </si>
-  <si>
     <t>Distribution requirements</t>
   </si>
   <si>
-    <t>Total 3 and 4 family homes</t>
-  </si>
-  <si>
-    <t>Requirement for (3 and 4 family homes)</t>
+    <t>Realized distribution</t>
+  </si>
+  <si>
+    <t>Total built</t>
   </si>
 </sst>
 </file>
@@ -152,15 +181,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,21 +523,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B8FB5E-E762-4AE1-81DE-835418022A2F}">
-  <dimension ref="B2:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -530,19 +556,32 @@
       <c r="G2" t="s">
         <v>8</v>
       </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="1">
+        <v>36.231884057971001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>99.637681159420268</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45.289855072463759</v>
+      </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>-1.7763568394002505E-15</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>108.69565217391303</v>
+      </c>
+      <c r="H3">
+        <f>SUM(C3:F3)</f>
+        <v>181.15942028985501</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
@@ -551,7 +590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -568,18 +607,19 @@
         <v>900</v>
       </c>
       <c r="G4">
-        <f>-1000*(1 - 0.15)</f>
-        <v>-850</v>
+        <f>1000*(1 - 0.15)</f>
+        <v>850</v>
       </c>
       <c r="I4">
-        <f>SUMPRODUCT(C3:G3,C4:G4)</f>
-        <v>50</v>
+        <f>SUMPRODUCT(C3:F3,C4:F4)</f>
+        <v>92391.304347826081</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <f>G3*G4</f>
+        <v>92391.304347826081</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>7</v>
       </c>
@@ -601,13 +641,13 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2">
         <f>SUMPRODUCT(C3:G3,C5:G5)</f>
-        <v>163000</v>
+        <v>14999999.999999996</v>
       </c>
       <c r="J5" s="2">
         <v>15000000</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -628,10 +668,10 @@
       </c>
       <c r="H6" s="3">
         <f>SUMPRODUCT(C3:G3,C6:G6)</f>
-        <v>2800</v>
+        <v>314311.5942028985</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="F7" s="4" t="s">
         <v>12</v>
       </c>
@@ -639,42 +679,38 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C8">
-        <f>0.2*C10</f>
-        <v>0.4</v>
-      </c>
-      <c r="D8">
-        <f>0.2*C10</f>
-        <v>0.4</v>
+      <c r="C9">
+        <f>C3</f>
+        <v>36.231884057971001</v>
+      </c>
+      <c r="D9">
+        <f>D3</f>
+        <v>99.637681159420268</v>
+      </c>
+      <c r="E9">
+        <f>SUM(E3:F3)</f>
+        <v>45.289855072463759</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10">
-        <f>SUM(C3:G3)</f>
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <f>SUM(E3:F3)</f>
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <f>0.25*C10</f>
-        <v>0.5</v>
+        <f>0.2*H3</f>
+        <v>36.231884057971001</v>
+      </c>
+      <c r="D10">
+        <f>0.2*H3</f>
+        <v>36.231884057971001</v>
+      </c>
+      <c r="E10">
+        <f>0.25*H3</f>
+        <v>45.289855072463752</v>
       </c>
     </row>
   </sheetData>
